--- a/benchmark/new_results/yes_cache1.xlsx
+++ b/benchmark/new_results/yes_cache1.xlsx
@@ -515,37 +515,37 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="H2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7627</v>
+        <v>6.2946</v>
       </c>
       <c r="J2" t="n">
-        <v>147.87</v>
+        <v>158.87</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9668</v>
+        <v>3.762</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6928</v>
+        <v>3.5964</v>
       </c>
       <c r="M2" t="n">
-        <v>1.7438</v>
+        <v>1.7189</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4972</v>
+        <v>5.9895</v>
       </c>
       <c r="O2" t="n">
-        <v>122.05</v>
+        <v>122.09</v>
       </c>
       <c r="P2" t="n">
-        <v>126.15</v>
+        <v>126.13</v>
       </c>
     </row>
     <row r="3">
@@ -565,37 +565,37 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>885</v>
+        <v>850</v>
       </c>
       <c r="H3" t="n">
-        <v>11.5</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>7.5308</v>
+        <v>7.4607</v>
       </c>
       <c r="J3" t="n">
-        <v>132.79</v>
+        <v>134.04</v>
       </c>
       <c r="K3" t="n">
-        <v>5.29</v>
+        <v>5.2691</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5369</v>
+        <v>4.5335</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0629</v>
+        <v>0.9742</v>
       </c>
       <c r="N3" t="n">
-        <v>6.9791</v>
+        <v>6.9959</v>
       </c>
       <c r="O3" t="n">
-        <v>147.26</v>
+        <v>147.48</v>
       </c>
       <c r="P3" t="n">
-        <v>152.97</v>
+        <v>153.11</v>
       </c>
     </row>
     <row r="4">
@@ -615,37 +615,37 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>975</v>
+        <v>220</v>
       </c>
       <c r="G4" t="n">
-        <v>4025</v>
+        <v>3968</v>
       </c>
       <c r="H4" t="n">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>35.0223</v>
+        <v>33.1373</v>
       </c>
       <c r="J4" t="n">
-        <v>142.77</v>
+        <v>150.89</v>
       </c>
       <c r="K4" t="n">
-        <v>18.5151</v>
+        <v>17.478</v>
       </c>
       <c r="L4" t="n">
-        <v>18.4155</v>
+        <v>17.4245</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0815</v>
+        <v>0.7179</v>
       </c>
       <c r="N4" t="n">
-        <v>34.2596</v>
+        <v>32.5739</v>
       </c>
       <c r="O4" t="n">
-        <v>159.58</v>
+        <v>160.32</v>
       </c>
       <c r="P4" t="n">
-        <v>161.23</v>
+        <v>162.14</v>
       </c>
     </row>
     <row r="5">
@@ -665,37 +665,37 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>993</v>
+        <v>214</v>
       </c>
       <c r="G5" t="n">
-        <v>4007</v>
+        <v>3974</v>
       </c>
       <c r="H5" t="n">
-        <v>19.86</v>
+        <v>4.28</v>
       </c>
       <c r="I5" t="n">
-        <v>34.9379</v>
+        <v>34.52</v>
       </c>
       <c r="J5" t="n">
-        <v>143.11</v>
+        <v>144.84</v>
       </c>
       <c r="K5" t="n">
-        <v>19.4216</v>
+        <v>18.0956</v>
       </c>
       <c r="L5" t="n">
-        <v>20.265</v>
+        <v>18.8165</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2146</v>
+        <v>1.1292</v>
       </c>
       <c r="N5" t="n">
-        <v>34.0744</v>
+        <v>33.6632</v>
       </c>
       <c r="O5" t="n">
-        <v>180.85</v>
+        <v>181.48</v>
       </c>
       <c r="P5" t="n">
-        <v>182.41</v>
+        <v>183.1</v>
       </c>
     </row>
     <row r="6">
@@ -715,37 +715,37 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2567</v>
+        <v>956</v>
       </c>
       <c r="G6" t="n">
-        <v>7433</v>
+        <v>7412</v>
       </c>
       <c r="H6" t="n">
-        <v>25.67</v>
+        <v>9.56</v>
       </c>
       <c r="I6" t="n">
-        <v>68.806</v>
+        <v>68.8398</v>
       </c>
       <c r="J6" t="n">
-        <v>145.34</v>
+        <v>145.26</v>
       </c>
       <c r="K6" t="n">
-        <v>34.3339</v>
+        <v>36.5947</v>
       </c>
       <c r="L6" t="n">
-        <v>34.6269</v>
+        <v>36.8975</v>
       </c>
       <c r="M6" t="n">
-        <v>2.504</v>
+        <v>2.3384</v>
       </c>
       <c r="N6" t="n">
-        <v>67.47150000000001</v>
+        <v>66.6459</v>
       </c>
       <c r="O6" t="n">
-        <v>195.26</v>
+        <v>196.4</v>
       </c>
       <c r="P6" t="n">
-        <v>198.57</v>
+        <v>199.48</v>
       </c>
     </row>
     <row r="7">
@@ -765,37 +765,37 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2621</v>
+        <v>987</v>
       </c>
       <c r="G7" t="n">
-        <v>7379</v>
+        <v>7448</v>
       </c>
       <c r="H7" t="n">
-        <v>26.21</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>74.4579</v>
+        <v>75.22190000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>134.3</v>
+        <v>132.94</v>
       </c>
       <c r="K7" t="n">
-        <v>41.014</v>
+        <v>39.7764</v>
       </c>
       <c r="L7" t="n">
-        <v>41.5719</v>
+        <v>40.3818</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8577</v>
+        <v>2.1579</v>
       </c>
       <c r="N7" t="n">
-        <v>71.24639999999999</v>
+        <v>73.74590000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>215.85</v>
+        <v>217.97</v>
       </c>
       <c r="P7" t="n">
-        <v>218.28</v>
+        <v>220.68</v>
       </c>
     </row>
     <row r="8">
@@ -815,37 +815,37 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>910</v>
+        <v>893</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9211</v>
+        <v>4.0271</v>
       </c>
       <c r="J8" t="n">
-        <v>255.03</v>
+        <v>248.32</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2774</v>
+        <v>2.3158</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2132</v>
+        <v>2.2364</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9994</v>
+        <v>0.7231</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6347</v>
+        <v>3.723</v>
       </c>
       <c r="O8" t="n">
-        <v>168</v>
+        <v>167.08</v>
       </c>
       <c r="P8" t="n">
-        <v>172.8</v>
+        <v>174.92</v>
       </c>
     </row>
     <row r="9">
@@ -865,37 +865,37 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>910</v>
+        <v>845</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9154</v>
+        <v>3.9304</v>
       </c>
       <c r="J9" t="n">
-        <v>255.4</v>
+        <v>254.43</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5989</v>
+        <v>2.4857</v>
       </c>
       <c r="L9" t="n">
-        <v>2.2566</v>
+        <v>2.2063</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2471</v>
+        <v>0.8084</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4278</v>
+        <v>3.4523</v>
       </c>
       <c r="O9" t="n">
-        <v>173.48</v>
+        <v>179.82</v>
       </c>
       <c r="P9" t="n">
-        <v>182.89</v>
+        <v>189.45</v>
       </c>
     </row>
     <row r="10">
@@ -909,43 +909,43 @@
         <v>5000</v>
       </c>
       <c r="D10" t="n">
-        <v>4848</v>
+        <v>5000</v>
       </c>
       <c r="E10" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>934</v>
+        <v>262</v>
       </c>
       <c r="G10" t="n">
-        <v>3914</v>
+        <v>3882</v>
       </c>
       <c r="H10" t="n">
-        <v>19.27</v>
+        <v>5.24</v>
       </c>
       <c r="I10" t="n">
-        <v>120.3228</v>
+        <v>16.5553</v>
       </c>
       <c r="J10" t="n">
-        <v>40.29</v>
+        <v>302.02</v>
       </c>
       <c r="K10" t="n">
-        <v>17.1885</v>
+        <v>8.581799999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>17.0739</v>
+        <v>8.567600000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5402</v>
+        <v>0.7038</v>
       </c>
       <c r="N10" t="n">
-        <v>32.9327</v>
+        <v>15.9153</v>
       </c>
       <c r="O10" t="n">
-        <v>158.81</v>
+        <v>170.11</v>
       </c>
       <c r="P10" t="n">
-        <v>167.02</v>
+        <v>171.77</v>
       </c>
     </row>
     <row r="11">
@@ -959,43 +959,43 @@
         <v>5000</v>
       </c>
       <c r="D11" t="n">
-        <v>4489</v>
+        <v>5000</v>
       </c>
       <c r="E11" t="n">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>894</v>
+        <v>231</v>
       </c>
       <c r="G11" t="n">
-        <v>3595</v>
+        <v>3937</v>
       </c>
       <c r="H11" t="n">
-        <v>19.92</v>
+        <v>4.62</v>
       </c>
       <c r="I11" t="n">
-        <v>120.9427</v>
+        <v>17.8605</v>
       </c>
       <c r="J11" t="n">
-        <v>37.12</v>
+        <v>279.95</v>
       </c>
       <c r="K11" t="n">
-        <v>15.1366</v>
+        <v>9.498699999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>15.1263</v>
+        <v>9.374700000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1245</v>
+        <v>0.9771</v>
       </c>
       <c r="N11" t="n">
-        <v>28.7113</v>
+        <v>16.9481</v>
       </c>
       <c r="O11" t="n">
-        <v>178.82</v>
+        <v>187.38</v>
       </c>
       <c r="P11" t="n">
-        <v>185.35</v>
+        <v>189.92</v>
       </c>
     </row>
     <row r="12">
@@ -1009,43 +1009,43 @@
         <v>10000</v>
       </c>
       <c r="D12" t="n">
-        <v>9423</v>
+        <v>10000</v>
       </c>
       <c r="E12" t="n">
-        <v>577</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2368</v>
+        <v>947</v>
       </c>
       <c r="G12" t="n">
-        <v>7055</v>
+        <v>7476</v>
       </c>
       <c r="H12" t="n">
-        <v>25.13</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>121.9927</v>
+        <v>41.3889</v>
       </c>
       <c r="J12" t="n">
-        <v>77.23999999999999</v>
+        <v>241.61</v>
       </c>
       <c r="K12" t="n">
-        <v>54.2447</v>
+        <v>18.891</v>
       </c>
       <c r="L12" t="n">
-        <v>52.9546</v>
+        <v>17.4989</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5166</v>
+        <v>1.7954</v>
       </c>
       <c r="N12" t="n">
-        <v>120.4884</v>
+        <v>39.9658</v>
       </c>
       <c r="O12" t="n">
-        <v>195.11</v>
+        <v>196.78</v>
       </c>
       <c r="P12" t="n">
-        <v>197.69</v>
+        <v>200.83</v>
       </c>
     </row>
     <row r="13">
@@ -1059,43 +1059,43 @@
         <v>10000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E13" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>7390</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>9.49</v>
       </c>
       <c r="I13" t="n">
-        <v>124.7394</v>
+        <v>50.651</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>197.43</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>25.4867</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>25.5793</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.7822</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>49.203</v>
       </c>
       <c r="O13" t="n">
-        <v>217.45</v>
+        <v>218.34</v>
       </c>
       <c r="P13" t="n">
-        <v>218.77</v>
+        <v>221.39</v>
       </c>
     </row>
     <row r="14">
@@ -1115,37 +1115,37 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="H14" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="I14" t="n">
-        <v>10.4915</v>
+        <v>2.9358</v>
       </c>
       <c r="J14" t="n">
-        <v>95.31999999999999</v>
+        <v>340.62</v>
       </c>
       <c r="K14" t="n">
-        <v>6.0034</v>
+        <v>1.7843</v>
       </c>
       <c r="L14" t="n">
-        <v>6.1191</v>
+        <v>1.8299</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4315</v>
+        <v>0.8244</v>
       </c>
       <c r="N14" t="n">
-        <v>9.9915</v>
+        <v>2.6036</v>
       </c>
       <c r="O14" t="n">
-        <v>185.54</v>
+        <v>178.09</v>
       </c>
       <c r="P14" t="n">
-        <v>187.11</v>
+        <v>184.29</v>
       </c>
     </row>
     <row r="15">
@@ -1165,37 +1165,37 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>922</v>
+        <v>884</v>
       </c>
       <c r="H15" t="n">
-        <v>7.8</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>10.8445</v>
+        <v>2.6944</v>
       </c>
       <c r="J15" t="n">
-        <v>92.20999999999999</v>
+        <v>371.14</v>
       </c>
       <c r="K15" t="n">
-        <v>7.1394</v>
+        <v>1.664</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9351</v>
+        <v>1.6973</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1962</v>
+        <v>0.6653</v>
       </c>
       <c r="N15" t="n">
-        <v>9.6972</v>
+        <v>2.162</v>
       </c>
       <c r="O15" t="n">
-        <v>200.99</v>
+        <v>186.07</v>
       </c>
       <c r="P15" t="n">
-        <v>204.54</v>
+        <v>198.3</v>
       </c>
     </row>
     <row r="16">
@@ -1215,37 +1215,37 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>973</v>
+        <v>295</v>
       </c>
       <c r="G16" t="n">
-        <v>4027</v>
+        <v>3989</v>
       </c>
       <c r="H16" t="n">
-        <v>19.46</v>
+        <v>5.9</v>
       </c>
       <c r="I16" t="n">
-        <v>48.9974</v>
+        <v>15.9264</v>
       </c>
       <c r="J16" t="n">
-        <v>102.05</v>
+        <v>313.94</v>
       </c>
       <c r="K16" t="n">
-        <v>25.7321</v>
+        <v>6.9152</v>
       </c>
       <c r="L16" t="n">
-        <v>25.8989</v>
+        <v>5.8801</v>
       </c>
       <c r="M16" t="n">
-        <v>2.408</v>
+        <v>0.6489</v>
       </c>
       <c r="N16" t="n">
-        <v>47.3995</v>
+        <v>15.2317</v>
       </c>
       <c r="O16" t="n">
-        <v>180.79</v>
+        <v>173.87</v>
       </c>
       <c r="P16" t="n">
-        <v>181.41</v>
+        <v>175.59</v>
       </c>
     </row>
     <row r="17">
@@ -1265,37 +1265,37 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>984</v>
+        <v>271</v>
       </c>
       <c r="G17" t="n">
-        <v>4016</v>
+        <v>3920</v>
       </c>
       <c r="H17" t="n">
-        <v>19.68</v>
+        <v>5.42</v>
       </c>
       <c r="I17" t="n">
-        <v>41.4286</v>
+        <v>20.0703</v>
       </c>
       <c r="J17" t="n">
-        <v>120.69</v>
+        <v>249.12</v>
       </c>
       <c r="K17" t="n">
-        <v>25.1859</v>
+        <v>10.453</v>
       </c>
       <c r="L17" t="n">
-        <v>26.4034</v>
+        <v>10.743</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1729</v>
+        <v>1.4001</v>
       </c>
       <c r="N17" t="n">
-        <v>39.111</v>
+        <v>18.8992</v>
       </c>
       <c r="O17" t="n">
-        <v>194.38</v>
+        <v>190.07</v>
       </c>
       <c r="P17" t="n">
-        <v>195.5</v>
+        <v>192.28</v>
       </c>
     </row>
     <row r="18">
@@ -1315,37 +1315,37 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2523</v>
+        <v>1042</v>
       </c>
       <c r="G18" t="n">
-        <v>7477</v>
+        <v>7452</v>
       </c>
       <c r="H18" t="n">
-        <v>25.23</v>
+        <v>10.42</v>
       </c>
       <c r="I18" t="n">
-        <v>31.3147</v>
+        <v>37.3255</v>
       </c>
       <c r="J18" t="n">
-        <v>319.34</v>
+        <v>267.91</v>
       </c>
       <c r="K18" t="n">
-        <v>13.904</v>
+        <v>18.7893</v>
       </c>
       <c r="L18" t="n">
-        <v>9.620799999999999</v>
+        <v>18.9397</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2947</v>
+        <v>1.3023</v>
       </c>
       <c r="N18" t="n">
-        <v>30.0962</v>
+        <v>35.9483</v>
       </c>
       <c r="O18" t="n">
-        <v>193.09</v>
+        <v>197.58</v>
       </c>
       <c r="P18" t="n">
-        <v>197.72</v>
+        <v>201.05</v>
       </c>
     </row>
     <row r="19">
@@ -1365,37 +1365,37 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2537</v>
+        <v>941</v>
       </c>
       <c r="G19" t="n">
-        <v>7463</v>
+        <v>7405</v>
       </c>
       <c r="H19" t="n">
-        <v>25.37</v>
+        <v>9.41</v>
       </c>
       <c r="I19" t="n">
-        <v>19.7517</v>
+        <v>39.2698</v>
       </c>
       <c r="J19" t="n">
-        <v>506.29</v>
+        <v>254.65</v>
       </c>
       <c r="K19" t="n">
-        <v>9.909800000000001</v>
+        <v>19.9293</v>
       </c>
       <c r="L19" t="n">
-        <v>9.889099999999999</v>
+        <v>20.0216</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1781</v>
+        <v>1.578</v>
       </c>
       <c r="N19" t="n">
-        <v>18.5527</v>
+        <v>37.6534</v>
       </c>
       <c r="O19" t="n">
-        <v>214.29</v>
+        <v>218.7</v>
       </c>
       <c r="P19" t="n">
-        <v>218.64</v>
+        <v>221.69</v>
       </c>
     </row>
   </sheetData>
